--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fileVersion appName="HCell" lastEdited="12.0" lowestEdited="12.0" rupBuild="0.535"/>
+  <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.12458"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294934950" windowHeight="6150"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -21,6 +21,105 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
   <x:si>
+    <x:t>Icon/Icon_Item_Box_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Equip_Hat_1</x:t>
   </x:si>
   <x:si>
@@ -28,105 +127,6 @@
   </x:si>
   <x:si>
     <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Box_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -228,16 +228,16 @@
   <x:borders count="2">
     <x:border>
       <x:left>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:left>
       <x:right>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:right>
       <x:top>
         <x:color auto="1"/>
       </x:top>
       <x:bottom>
-        <x:color rgb="ff000000"/>
+        <x:color auto="1"/>
       </x:bottom>
     </x:border>
     <x:border>
@@ -261,8 +261,8 @@
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="16">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
@@ -319,6 +319,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -401,6 +402,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -435,6 +437,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -479,6 +482,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -522,6 +526,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -606,6 +611,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -626,6 +632,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -656,6 +663,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -904,9 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetPr codeName="Sheet1">
-    <x:outlinePr applyStyles="0" summaryBelow="0" summaryRight="1" showOutlineSymbols="1"/>
-  </x:sheetPr>
+  <x:sheetPr codeName="Sheet1"/>
   <x:dimension ref="A1:M35"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
@@ -921,80 +927,80 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:8" ht="13.199999999999999">
+      <x:c r="A2" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="13.19999999999999928946">
-      <x:c r="A2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>6</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>23</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>24</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1003,7 +1009,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1013,19 +1019,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1034,7 +1040,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1044,19 +1050,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1065,7 +1071,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1074,19 +1080,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1095,7 +1101,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1105,19 +1111,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B8" s="3" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1126,7 +1132,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -2305,7 +2311,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438477" right="0.69986110925674438477" top="0.75" bottom="0.75" header="0.30000001192092895508" footer="0.30000001192092895508"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -19,7 +19,100 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="56">
+  <x:si>
+    <x:t>Item_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Box_1</x:t>
   </x:si>
@@ -27,39 +120,30 @@
     <x:t>Icon/Icon_Item_Gold_1</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
+    <x:t>Item_Aqua</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
   </x:si>
   <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Corn_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
@@ -69,64 +153,40 @@
     <x:t>ItemType</x:t>
   </x:si>
   <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
   </x:si>
   <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+    <x:t>수분을 얼려서 얼음을 만들어 공격한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기초적인 공격마법으로 마나 덩어리로 적을 공격한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전기를 일으켜 공격한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매직 애로우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아쿠아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물을 생성하여 공격한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불꽃을 일으켜 공격한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Aqua</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -920,87 +980,88 @@
     <x:col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="50.7109375" style="2" customWidth="1"/>
     <x:col min="4" max="4" width="26.5703125" style="2" customWidth="1"/>
-    <x:col min="5" max="7" width="12.5703125" style="2"/>
+    <x:col min="5" max="5" width="12.5703125" style="2"/>
+    <x:col min="6" max="7" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
     <x:col min="8" max="8" width="28.42578125" style="2" customWidth="1"/>
     <x:col min="9" max="16384" width="12.5703125" style="2"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="s">
         <x:v>26</x:v>
       </x:c>
-      <x:c r="B3" s="11" t="s">
-        <x:v>17</x:v>
-      </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>8</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>9</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>27</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1009,7 +1070,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1019,19 +1080,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1040,7 +1101,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1050,19 +1111,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1071,7 +1132,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1080,19 +1141,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1101,7 +1162,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1111,19 +1172,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B8" s="3" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1132,7 +1193,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1141,14 +1202,30 @@
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A9" s="6"/>
-      <x:c r="B9" s="6"/>
-      <x:c r="C9" s="6"/>
-      <x:c r="D9" s="4"/>
-      <x:c r="E9" s="4"/>
-      <x:c r="F9" s="4"/>
-      <x:c r="G9" s="4"/>
-      <x:c r="H9" s="4"/>
+      <x:c r="A9" s="6" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F9" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G9" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="4" t="s">
+        <x:v>47</x:v>
+      </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>
@@ -1156,14 +1233,30 @@
       <x:c r="M9" s="4"/>
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A10" s="1"/>
-      <x:c r="B10" s="1"/>
-      <x:c r="C10" s="1"/>
-      <x:c r="D10" s="4"/>
-      <x:c r="E10" s="4"/>
-      <x:c r="F10" s="4"/>
-      <x:c r="G10" s="4"/>
-      <x:c r="H10" s="4"/>
+      <x:c r="A10" s="6" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E10" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F10" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G10" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" s="4" t="s">
+        <x:v>55</x:v>
+      </x:c>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
       <x:c r="K10" s="4"/>
@@ -1171,14 +1264,30 @@
       <x:c r="M10" s="4"/>
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A11" s="1"/>
-      <x:c r="B11" s="1"/>
-      <x:c r="C11" s="1"/>
-      <x:c r="D11" s="4"/>
-      <x:c r="E11" s="4"/>
-      <x:c r="F11" s="4"/>
-      <x:c r="G11" s="4"/>
-      <x:c r="H11" s="4"/>
+      <x:c r="A11" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E11" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F11" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="I11" s="4"/>
       <x:c r="J11" s="4"/>
       <x:c r="K11" s="4"/>
@@ -1186,14 +1295,30 @@
       <x:c r="M11" s="4"/>
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6"/>
-      <x:c r="B12" s="6"/>
-      <x:c r="C12" s="6"/>
-      <x:c r="D12" s="4"/>
-      <x:c r="E12" s="4"/>
-      <x:c r="F12" s="4"/>
-      <x:c r="G12" s="4"/>
-      <x:c r="H12" s="4"/>
+      <x:c r="A12" s="6" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E12" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F12" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G12" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H12" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="4"/>
       <x:c r="K12" s="4"/>
@@ -1201,14 +1326,30 @@
       <x:c r="M12" s="4"/>
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A13" s="3"/>
-      <x:c r="B13" s="3"/>
-      <x:c r="C13" s="3"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
-      <x:c r="H13" s="4"/>
+      <x:c r="A13" s="6" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B13" s="3" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E13" s="4" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F13" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="4" t="s">
+        <x:v>48</x:v>
+      </x:c>
       <x:c r="I13" s="4"/>
       <x:c r="J13" s="4"/>
       <x:c r="K13" s="4"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="16332" windowHeight="6744"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,99 +19,192 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="56">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="65">
+  <x:si>
+    <x:t>Item_Aqua</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Aqua</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매직 애로우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1:1,Item_Corn_1:20,Item_Gold_1:100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아쿠아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RandomItemBox</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SummonMonster</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_bear_1:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불꽃을 일으켜 공격한다</x:t>
+  </x:si>
   <x:si>
     <x:t>Item_Lightning</x:t>
   </x:si>
   <x:si>
-    <x:t>라이트닝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
+    <x:t>Item_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>물을 생성하여 공격한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>전기를 일으켜 공격한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기초적인 공격마법으로 마나 덩어리로 적을 공격한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수분을 얼려서 얼음을 만들어 공격한다</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Box_1</x:t>
@@ -120,73 +213,7 @@
     <x:t>Icon/Icon_Item_Gold_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Aqua</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수분을 얼려서 얼음을 만들어 공격한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기초적인 공격마법으로 마나 덩어리로 적을 공격한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전기를 일으켜 공격한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매직 애로우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아쿠아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>물을 생성하여 공격한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불꽃을 일으켜 공격한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Aqua</x:t>
+    <x:t>UseItemParameterList</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -983,85 +1010,99 @@
     <x:col min="5" max="5" width="12.5703125" style="2"/>
     <x:col min="6" max="7" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
     <x:col min="8" max="8" width="28.42578125" style="2" customWidth="1"/>
-    <x:col min="9" max="16384" width="12.5703125" style="2"/>
+    <x:col min="9" max="9" width="14.84765625" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="10" max="10" width="49.26953125" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="11" max="16384" width="12.5703125" style="2"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="13.199999999999999">
+        <x:v>51</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:10" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:10" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="11" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>19</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>15</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>36</x:v>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="J3" s="12" t="s">
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1070,29 +1111,33 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I4" s="4" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="J4" s="5" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="I4" s="4"/>
-      <x:c r="J4" s="4"/>
       <x:c r="K4" s="4"/>
       <x:c r="L4" s="4"/>
       <x:c r="M4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1101,7 +1146,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1111,19 +1156,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1132,28 +1177,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="I6" s="4"/>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I6" s="4" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="J6" s="2">
+        <x:v>700</x:v>
+      </x:c>
       <x:c r="K6" s="4"/>
       <x:c r="L6" s="4"/>
       <x:c r="M6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="D7" s="4" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1162,29 +1212,33 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="I7" s="4"/>
-      <x:c r="J7" s="4"/>
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="I7" s="4" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J7" s="4">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="K7" s="4"/>
       <x:c r="L7" s="4"/>
       <x:c r="M7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>16</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1193,29 +1247,33 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="4"/>
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I8" s="4" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="J8" s="4" t="s">
+        <x:v>46</x:v>
+      </x:c>
       <x:c r="K8" s="4"/>
       <x:c r="L8" s="4"/>
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>35</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>51</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>1</x:v>
@@ -1224,7 +1282,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
@@ -1234,19 +1292,19 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="6" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>52</x:v>
-      </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F10" s="4">
         <x:v>1</x:v>
@@ -1255,7 +1313,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H10" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
@@ -1265,19 +1323,19 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F11" s="4">
         <x:v>1</x:v>
@@ -1286,7 +1344,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="I11" s="4"/>
       <x:c r="J11" s="4"/>
@@ -1296,19 +1354,19 @@
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F12" s="4">
         <x:v>1</x:v>
@@ -1317,7 +1375,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="4"/>
@@ -1327,19 +1385,19 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F13" s="4">
         <x:v>1</x:v>
@@ -1348,7 +1406,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H13" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I13" s="4"/>
       <x:c r="J13" s="4"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="16332" windowHeight="6744"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -21,187 +21,187 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="65">
   <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1:1,Item_Corn_1:20,Item_Gold_1:100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매직 애로우</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아쿠아</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Aqua</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Aqua</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
     <x:t>ItemType</x:t>
   </x:si>
   <x:si>
-    <x:t>IconPath</x:t>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Ice</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Fire</x:t>
   </x:si>
   <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Aqua</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
     <x:t>string[]</x:t>
   </x:si>
   <x:si>
-    <x:t>매직 애로우</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>라이트닝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1:1,Item_Corn_1:20,Item_Gold_1:100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아쿠아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
+    <x:t>Icon/Icon_Item_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기초적인 공격마법으로 마나 덩어리로 적을 공격한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>불꽃을 일으켜 공격한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RandomItemBox</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
   </x:si>
   <x:si>
     <x:t>SellingPrice</x:t>
   </x:si>
   <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RandomItemBox</x:t>
-  </x:si>
-  <x:si>
     <x:t>SummonMonster</x:t>
   </x:si>
   <x:si>
-    <x:t>MaxStackCount</x:t>
+    <x:t>StatChangeHp</x:t>
   </x:si>
   <x:si>
     <x:t>mob_bear_1:2</x:t>
   </x:si>
   <x:si>
-    <x:t>StatChangeHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>불꽃을 일으켜 공격한다</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Lightning</x:t>
   </x:si>
   <x:si>
     <x:t>Item_MagicArrow</x:t>
   </x:si>
   <x:si>
+    <x:t>전기를 일으켜 공격한다</x:t>
+  </x:si>
+  <x:si>
     <x:t>물을 생성하여 공격한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>전기를 일으켜 공격한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기초적인 공격마법으로 마나 덩어리로 적을 공격한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_MagicArrow</x:t>
   </x:si>
   <x:si>
     <x:t>수분을 얼려서 얼음을 만들어 공격한다</x:t>
@@ -372,9 +372,6 @@
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -395,6 +392,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1017,74 +1017,74 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:10" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:10" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="H3" s="13" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="I3" s="12" t="s">
+    </x:row>
+    <x:row r="3" spans="1:10" s="11" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C3" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D3" s="13" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="E3" s="12" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="J3" s="12" t="s">
+      <x:c r="F3" s="12" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G3" s="12" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H3" s="12" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="J3" s="11" t="s">
         <x:v>64</x:v>
       </x:c>
     </x:row>
@@ -1093,16 +1093,16 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1114,10 +1114,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="I4" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="J4" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K4" s="4"/>
       <x:c r="L4" s="4"/>
@@ -1125,19 +1125,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1156,19 +1156,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1177,7 +1177,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="I6" s="4" t="s">
         <x:v>49</x:v>
@@ -1191,19 +1191,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1212,10 +1212,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="I7" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="J7" s="4">
         <x:v>20</x:v>
@@ -1225,20 +1225,20 @@
       <x:c r="M7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A8" s="15" t="s">
-        <x:v>50</x:v>
+      <x:c r="A8" s="14" t="s">
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1250,10 +1250,10 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="I8" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="J8" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="K8" s="4"/>
       <x:c r="L8" s="4"/>
@@ -1261,19 +1261,19 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>54</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>1</x:v>
@@ -1282,7 +1282,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
@@ -1292,19 +1292,19 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F10" s="4">
         <x:v>1</x:v>
@@ -1313,7 +1313,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H10" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
@@ -1323,19 +1323,19 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F11" s="4">
         <x:v>1</x:v>
@@ -1344,7 +1344,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H11" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="I11" s="4"/>
       <x:c r="J11" s="4"/>
@@ -1354,19 +1354,19 @@
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F12" s="4">
         <x:v>1</x:v>
@@ -1375,7 +1375,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H12" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="4"/>
@@ -1385,19 +1385,19 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F13" s="4">
         <x:v>1</x:v>
@@ -1406,7 +1406,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H13" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="I13" s="4"/>
       <x:c r="J13" s="4"/>
@@ -1445,104 +1445,104 @@
       <x:c r="M15" s="4"/>
     </x:row>
     <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A16" s="7"/>
-      <x:c r="B16" s="7"/>
-      <x:c r="C16" s="7"/>
+      <x:c r="A16" s="15"/>
+      <x:c r="B16" s="15"/>
+      <x:c r="C16" s="15"/>
     </x:row>
     <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A17" s="8"/>
-      <x:c r="B17" s="8"/>
-      <x:c r="C17" s="8"/>
+      <x:c r="A17" s="7"/>
+      <x:c r="B17" s="7"/>
+      <x:c r="C17" s="7"/>
     </x:row>
     <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A18" s="8"/>
-      <x:c r="B18" s="8"/>
-      <x:c r="C18" s="8"/>
+      <x:c r="A18" s="7"/>
+      <x:c r="B18" s="7"/>
+      <x:c r="C18" s="7"/>
     </x:row>
     <x:row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A19" s="8"/>
-      <x:c r="B19" s="8"/>
-      <x:c r="C19" s="8"/>
+      <x:c r="A19" s="7"/>
+      <x:c r="B19" s="7"/>
+      <x:c r="C19" s="7"/>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A20" s="8"/>
-      <x:c r="B20" s="8"/>
-      <x:c r="C20" s="8"/>
+      <x:c r="A20" s="7"/>
+      <x:c r="B20" s="7"/>
+      <x:c r="C20" s="7"/>
     </x:row>
     <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A21" s="8"/>
-      <x:c r="B21" s="8"/>
-      <x:c r="C21" s="8"/>
+      <x:c r="A21" s="7"/>
+      <x:c r="B21" s="7"/>
+      <x:c r="C21" s="7"/>
     </x:row>
     <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A22" s="8"/>
-      <x:c r="B22" s="8"/>
-      <x:c r="C22" s="8"/>
+      <x:c r="A22" s="7"/>
+      <x:c r="B22" s="7"/>
+      <x:c r="C22" s="7"/>
     </x:row>
     <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A23" s="8"/>
-      <x:c r="B23" s="8"/>
-      <x:c r="C23" s="8"/>
+      <x:c r="A23" s="7"/>
+      <x:c r="B23" s="7"/>
+      <x:c r="C23" s="7"/>
     </x:row>
     <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A24" s="8"/>
-      <x:c r="B24" s="8"/>
-      <x:c r="C24" s="8"/>
+      <x:c r="A24" s="7"/>
+      <x:c r="B24" s="7"/>
+      <x:c r="C24" s="7"/>
     </x:row>
     <x:row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A25" s="8"/>
-      <x:c r="B25" s="8"/>
-      <x:c r="C25" s="8"/>
+      <x:c r="A25" s="7"/>
+      <x:c r="B25" s="7"/>
+      <x:c r="C25" s="7"/>
     </x:row>
     <x:row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A26" s="9"/>
-      <x:c r="B26" s="9"/>
-      <x:c r="C26" s="9"/>
+      <x:c r="A26" s="8"/>
+      <x:c r="B26" s="8"/>
+      <x:c r="C26" s="8"/>
     </x:row>
     <x:row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A27" s="9"/>
-      <x:c r="B27" s="9"/>
-      <x:c r="C27" s="9"/>
+      <x:c r="A27" s="8"/>
+      <x:c r="B27" s="8"/>
+      <x:c r="C27" s="8"/>
     </x:row>
     <x:row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A28" s="9"/>
-      <x:c r="B28" s="9"/>
-      <x:c r="C28" s="9"/>
+      <x:c r="A28" s="8"/>
+      <x:c r="B28" s="8"/>
+      <x:c r="C28" s="8"/>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A29" s="9"/>
-      <x:c r="B29" s="9"/>
-      <x:c r="C29" s="9"/>
+      <x:c r="A29" s="8"/>
+      <x:c r="B29" s="8"/>
+      <x:c r="C29" s="8"/>
     </x:row>
     <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A30" s="9"/>
-      <x:c r="B30" s="9"/>
-      <x:c r="C30" s="9"/>
+      <x:c r="A30" s="8"/>
+      <x:c r="B30" s="8"/>
+      <x:c r="C30" s="8"/>
     </x:row>
     <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A31" s="9"/>
-      <x:c r="B31" s="9"/>
-      <x:c r="C31" s="9"/>
+      <x:c r="A31" s="8"/>
+      <x:c r="B31" s="8"/>
+      <x:c r="C31" s="8"/>
     </x:row>
     <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="10"/>
-      <x:c r="B32" s="10"/>
-      <x:c r="C32" s="10"/>
+      <x:c r="A32" s="9"/>
+      <x:c r="B32" s="9"/>
+      <x:c r="C32" s="9"/>
     </x:row>
     <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A33" s="10"/>
-      <x:c r="B33" s="10"/>
-      <x:c r="C33" s="10"/>
+      <x:c r="A33" s="9"/>
+      <x:c r="B33" s="9"/>
+      <x:c r="C33" s="9"/>
     </x:row>
     <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A34" s="10"/>
-      <x:c r="B34" s="10"/>
-      <x:c r="C34" s="10"/>
+      <x:c r="A34" s="9"/>
+      <x:c r="B34" s="9"/>
+      <x:c r="C34" s="9"/>
     </x:row>
     <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A35" s="10"/>
-      <x:c r="B35" s="10"/>
-      <x:c r="C35" s="10"/>
+      <x:c r="A35" s="9"/>
+      <x:c r="B35" s="9"/>
+      <x:c r="C35" s="9"/>
     </x:row>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22788" windowHeight="8520"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="16332" windowHeight="6744"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,111 +19,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="65">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="53">
+  <x:si>
+    <x:t>먹으면 랜덤한 이벤트가 발생한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>기초적인 공격마법으로 마나 덩어리로 적을 공격한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>라이트닝</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Fire</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Ice</x:t>
+  </x:si>
   <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Equip_Hat_1:1,Item_Corn_1:20,Item_Gold_1:100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
+    <x:t>파이어</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_MagicArrow</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Wand_DmgUp_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemParameterList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수분을 얼려서 얼음을 만들어 공격한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>먹으면 체력을 300회복한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Aqua</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Wand_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Heart_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Wand_DmgUp_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Chest_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Wand_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아쿠아</x:t>
   </x:si>
   <x:si>
     <x:t>매직 애로우</x:t>
   </x:si>
   <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
     <x:t>Grade</x:t>
   </x:si>
   <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
     <x:t>Normal</x:t>
   </x:si>
   <x:si>
-    <x:t>라이트닝</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파이어</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아쿠아</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Ice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Fire</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Aqua</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
+    <x:t>Item_Chest_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Heart_1</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Aqua</x:t>
@@ -132,88 +138,46 @@
     <x:t>ItemType</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Ice</x:t>
+  </x:si>
+  <x:si>
     <x:t>UseItemType</x:t>
   </x:si>
   <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Ice</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Fire</x:t>
   </x:si>
   <x:si>
     <x:t>string[]</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Item_MagicArrow</x:t>
-  </x:si>
-  <x:si>
-    <x:t>기초적인 공격마법으로 마나 덩어리로 적을 공격한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Lightning</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
+    <x:t>Item_Lightning</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
   </x:si>
   <x:si>
     <x:t>불꽃을 일으켜 공격한다</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RandomItemBox</x:t>
+    <x:t>전기를 일으켜 공격한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
   </x:si>
   <x:si>
     <x:t>MaxStackCount</x:t>
   </x:si>
   <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SummonMonster</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_bear_1:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Lightning</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_MagicArrow</x:t>
   </x:si>
   <x:si>
-    <x:t>전기를 일으켜 공격한다</x:t>
-  </x:si>
-  <x:si>
     <x:t>물을 생성하여 공격한다</x:t>
   </x:si>
   <x:si>
-    <x:t>수분을 얼려서 얼음을 만들어 공격한다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Box_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemParameterList</x:t>
+    <x:t>먹으면 공격력과 이동속도가 소폭 증가한다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>먹으면 공격력과 이동속도가 대폭 증가한다</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -262,7 +226,7 @@
       <x:color rgb="ff008000"/>
     </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -284,13 +248,13 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffffffff"/>
-        <x:bgColor rgb="ffffc000"/>
+        <x:bgColor rgb="ffd86dcd"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffffffff"/>
-        <x:bgColor rgb="ffd86dcd"/>
+        <x:bgColor rgb="ffffc000"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -303,12 +267,6 @@
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffd2f2db"/>
         <x:bgColor indexed="64"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffffff00"/>
-        <x:bgColor rgb="ffd86dcd"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -366,13 +324,10 @@
     <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -390,11 +345,14 @@
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+    <x:xf numFmtId="49" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1000,10 +958,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:M35"/>
+  <x:dimension ref="A1:M30"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="19.42578125" style="2" customWidth="1"/>
+    <x:col min="1" max="1" width="20.47265625" style="2" bestFit="1" customWidth="1"/>
     <x:col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="50.7109375" style="2" customWidth="1"/>
     <x:col min="4" max="4" width="26.5703125" style="2" customWidth="1"/>
@@ -1017,16 +975,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:10" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
         <x:v>5</x:v>
@@ -1041,10 +999,10 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
         <x:v>5</x:v>
@@ -1053,100 +1011,96 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:10" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="10" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B3" s="10" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:10" s="10" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="9" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B3" s="9" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D3" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H3" s="11" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C3" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="13" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E3" s="12" t="s">
+      <x:c r="I3" s="10" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J3" s="10" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="F3" s="12" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G3" s="12" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H3" s="12" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="I3" s="11" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="J3" s="11" t="s">
-        <x:v>64</x:v>
-      </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A4" s="3" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>27</x:v>
+      <x:c r="A4" s="5" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="s">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F4" s="4">
-        <x:v>20</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G4" s="4">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="I4" s="4" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J4" s="5" t="s">
-        <x:v>1</x:v>
-      </x:c>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I4" s="4"/>
+      <x:c r="J4" s="4"/>
       <x:c r="K4" s="4"/>
       <x:c r="L4" s="4"/>
       <x:c r="M4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A5" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="s">
+      <x:c r="A5" s="5" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D5" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F5" s="4">
-        <x:v>1000</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G5" s="4">
-        <x:v>1000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1156,133 +1110,113 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F6" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G6" s="4">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="4">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="I6" s="4" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="J6" s="2">
-        <x:v>700</x:v>
-      </x:c>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="I6" s="4"/>
+      <x:c r="J6" s="4"/>
       <x:c r="K6" s="4"/>
       <x:c r="L6" s="4"/>
       <x:c r="M6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A7" s="3" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B7" s="3" t="s">
+      <x:c r="A7" s="5" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D7" s="4" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F7" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G7" s="4">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="4" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C7" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E7" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F7" s="4">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G7" s="4">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H7" s="4" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="I7" s="4" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="J7" s="4">
-        <x:v>20</x:v>
-      </x:c>
+      <x:c r="I7" s="4"/>
+      <x:c r="J7" s="4"/>
       <x:c r="K7" s="4"/>
       <x:c r="L7" s="4"/>
       <x:c r="M7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A8" s="14" t="s">
-        <x:v>13</x:v>
+      <x:c r="A8" s="5" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F8" s="4">
-        <x:v>20</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G8" s="4">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="I8" s="4" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="J8" s="4" t="s">
-        <x:v>56</x:v>
-      </x:c>
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I8" s="4"/>
+      <x:c r="J8" s="4"/>
       <x:c r="K8" s="4"/>
       <x:c r="L8" s="4"/>
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A9" s="6" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="s">
+      <x:c r="A9" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C9" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="E9" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F9" s="4">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G9" s="4">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="D9" s="4"/>
+      <x:c r="E9" s="4"/>
+      <x:c r="F9" s="4"/>
+      <x:c r="G9" s="4"/>
       <x:c r="H9" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
@@ -1291,29 +1225,21 @@
       <x:c r="M9" s="4"/>
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A10" s="6" t="s">
+      <x:c r="A10" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D10" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E10" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F10" s="4">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G10" s="4">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="D10" s="4"/>
+      <x:c r="E10" s="4"/>
+      <x:c r="F10" s="4"/>
+      <x:c r="G10" s="4"/>
       <x:c r="H10" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
@@ -1321,153 +1247,73 @@
       <x:c r="L10" s="4"/>
       <x:c r="M10" s="4"/>
     </x:row>
-    <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A11" s="6" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B11" s="1" t="s">
+    <x:row r="11" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A11" s="15" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B11" s="13" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C11" s="13" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H11" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A12" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D11" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E11" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F11" s="4">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G11" s="4">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" s="4" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="I11" s="4"/>
-      <x:c r="J11" s="4"/>
-      <x:c r="K11" s="4"/>
-      <x:c r="L11" s="4"/>
-      <x:c r="M11" s="4"/>
-    </x:row>
-    <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="B12" s="6" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D12" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E12" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F12" s="4">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G12" s="4">
-        <x:v>0</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H12" s="4" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="I12" s="4"/>
-      <x:c r="J12" s="4"/>
-      <x:c r="K12" s="4"/>
-      <x:c r="L12" s="4"/>
-      <x:c r="M12" s="4"/>
-    </x:row>
-    <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A13" s="6" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B13" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C13" s="3" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="D13" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E13" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F13" s="4">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G13" s="4">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="4" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-      <x:c r="L13" s="4"/>
-      <x:c r="M13" s="4"/>
-    </x:row>
-    <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A14" s="1"/>
-      <x:c r="B14" s="1"/>
-      <x:c r="C14" s="1"/>
-      <x:c r="D14" s="4"/>
-      <x:c r="E14" s="4"/>
-      <x:c r="F14" s="4"/>
-      <x:c r="G14" s="4"/>
-      <x:c r="H14" s="4"/>
-      <x:c r="I14" s="4"/>
-      <x:c r="J14" s="4"/>
-      <x:c r="K14" s="4"/>
-      <x:c r="L14" s="4"/>
-      <x:c r="M14" s="4"/>
-    </x:row>
-    <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A15" s="1"/>
-      <x:c r="B15" s="1"/>
-      <x:c r="C15" s="1"/>
-      <x:c r="D15" s="4"/>
-      <x:c r="E15" s="4"/>
-      <x:c r="F15" s="4"/>
-      <x:c r="G15" s="4"/>
-      <x:c r="H15" s="4"/>
-      <x:c r="I15" s="4"/>
-      <x:c r="J15" s="4"/>
-      <x:c r="K15" s="4"/>
-      <x:c r="L15" s="4"/>
-      <x:c r="M15" s="4"/>
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A13" s="6"/>
+      <x:c r="B13" s="6"/>
+      <x:c r="C13" s="6"/>
+    </x:row>
+    <x:row r="14" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A14" s="6"/>
+      <x:c r="B14" s="6"/>
+      <x:c r="C14" s="6"/>
+    </x:row>
+    <x:row r="15" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A15" s="6"/>
+      <x:c r="B15" s="6"/>
+      <x:c r="C15" s="6"/>
     </x:row>
     <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A16" s="15"/>
-      <x:c r="B16" s="15"/>
-      <x:c r="C16" s="15"/>
+      <x:c r="A16" s="6"/>
+      <x:c r="B16" s="6"/>
+      <x:c r="C16" s="6"/>
     </x:row>
     <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A17" s="7"/>
-      <x:c r="B17" s="7"/>
-      <x:c r="C17" s="7"/>
+      <x:c r="A17" s="6"/>
+      <x:c r="B17" s="6"/>
+      <x:c r="C17" s="6"/>
     </x:row>
     <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A18" s="7"/>
-      <x:c r="B18" s="7"/>
-      <x:c r="C18" s="7"/>
+      <x:c r="A18" s="6"/>
+      <x:c r="B18" s="6"/>
+      <x:c r="C18" s="6"/>
     </x:row>
     <x:row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A19" s="7"/>
-      <x:c r="B19" s="7"/>
-      <x:c r="C19" s="7"/>
+      <x:c r="A19" s="6"/>
+      <x:c r="B19" s="6"/>
+      <x:c r="C19" s="6"/>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A20" s="7"/>
-      <x:c r="B20" s="7"/>
-      <x:c r="C20" s="7"/>
+      <x:c r="A20" s="6"/>
+      <x:c r="B20" s="6"/>
+      <x:c r="C20" s="6"/>
     </x:row>
     <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A21" s="7"/>
@@ -1495,9 +1341,9 @@
       <x:c r="C25" s="7"/>
     </x:row>
     <x:row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A26" s="8"/>
-      <x:c r="B26" s="8"/>
-      <x:c r="C26" s="8"/>
+      <x:c r="A26" s="7"/>
+      <x:c r="B26" s="7"/>
+      <x:c r="C26" s="7"/>
     </x:row>
     <x:row r="27" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A27" s="8"/>
@@ -1519,31 +1365,11 @@
       <x:c r="B30" s="8"/>
       <x:c r="C30" s="8"/>
     </x:row>
-    <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A31" s="8"/>
-      <x:c r="B31" s="8"/>
-      <x:c r="C31" s="8"/>
-    </x:row>
-    <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="9"/>
-      <x:c r="B32" s="9"/>
-      <x:c r="C32" s="9"/>
-    </x:row>
-    <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A33" s="9"/>
-      <x:c r="B33" s="9"/>
-      <x:c r="C33" s="9"/>
-    </x:row>
-    <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A34" s="9"/>
-      <x:c r="B34" s="9"/>
-      <x:c r="C34" s="9"/>
-    </x:row>
-    <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A35" s="9"/>
-      <x:c r="B35" s="9"/>
-      <x:c r="C35" s="9"/>
-    </x:row>
+    <x:row r="31" ht="15.75" customHeight="1"/>
+    <x:row r="32" ht="15.75" customHeight="1"/>
+    <x:row r="33" ht="15.75" customHeight="1"/>
+    <x:row r="34" ht="15.75" customHeight="1"/>
+    <x:row r="35" ht="15.75" customHeight="1"/>
     <x:row r="36" ht="15.75" customHeight="1"/>
     <x:row r="37" ht="15.75" customHeight="1"/>
     <x:row r="38" ht="15.75" customHeight="1"/>
@@ -2504,11 +2330,6 @@
     <x:row r="993" ht="15.75" customHeight="1"/>
     <x:row r="994" ht="15.75" customHeight="1"/>
     <x:row r="995" ht="15.75" customHeight="1"/>
-    <x:row r="996" ht="15.75" customHeight="1"/>
-    <x:row r="997" ht="15.75" customHeight="1"/>
-    <x:row r="998" ht="15.75" customHeight="1"/>
-    <x:row r="999" ht="15.75" customHeight="1"/>
-    <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
   <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
